--- a/testData/login_data.xlsx
+++ b/testData/login_data.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>username</t>
   </si>
@@ -75,15 +75,6 @@
   </si>
   <si>
     <t>valid</t>
-  </si>
-  <si>
-    <t>invalid</t>
-  </si>
-  <si>
-    <t>inValid</t>
-  </si>
-  <si>
-    <t>panda17@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -114,10 +105,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF17C6A3"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -152,18 +145,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -487,7 +482,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -498,7 +493,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -542,22 +537,25 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A8" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>